--- a/wisestar-client/public/templates/knowledge-point-import-template.xlsx
+++ b/wisestar-client/public/templates/knowledge-point-import-template.xlsx
@@ -413,16 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>学科名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>章节名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>小节名</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>知识点名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>排序(选填，数字越小越靠前)</t>
         </is>
@@ -431,21 +446,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>识字与写字</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>拼音入门</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>拼音王国</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>汉字笔顺</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100以内加减法</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>加法小站</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>进位加法</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/wisestar-client/public/templates/knowledge-point-import-template.xlsx
+++ b/wisestar-client/public/templates/knowledge-point-import-template.xlsx
@@ -413,8 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -442,6 +450,11 @@
           <t>排序(选填，数字越小越靠前)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>内容设置(选填，仅文本)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,8 +477,13 @@
           <t>拼音王国</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>掌握拼音字母读写与拼读规则，打好拼音基础</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -489,8 +507,13 @@
           <t>进位加法</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>个位相加满十向十位进 1，掌握竖式书写规范</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/wisestar-client/public/templates/knowledge-point-import-template.xlsx
+++ b/wisestar-client/public/templates/knowledge-point-import-template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -421,7 +421,9 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,6 +454,16 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>年级(选填，如：一年级)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>学期(选填，上/下)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>内容设置(选填，仅文本)</t>
         </is>
       </c>
@@ -477,10 +489,22 @@
           <t>拼音王国</t>
         </is>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>一年级</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>掌握拼音字母读写与拼读规则，打好拼音基础</t>
         </is>
@@ -507,12 +531,66 @@
           <t>进位加法</t>
         </is>
       </c>
-      <c r="E3">
-        <v>1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>一年级</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>个位相加满十向十位进 1，掌握竖式书写规范</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>识字与写字</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>字词辨析</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>形近字辨析</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>借助偏旁与字义对比区分易混字</t>
         </is>
       </c>
     </row>
